--- a/main/ig/StructureDefinition-as-bal-mss-app.xlsx
+++ b/main/ig/StructureDefinition-as-bal-mss-app.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T14:23:27+00:00</t>
+    <t>2026-09-29T07:26:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-bal-mss-app.xlsx
+++ b/main/ig/StructureDefinition-as-bal-mss-app.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T07:26:07+00:00</t>
+    <t>2026-09-30T08:41:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-bal-mss-app.xlsx
+++ b/main/ig/StructureDefinition-as-bal-mss-app.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapshot</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T08:41:32+00:00</t>
+    <t>2026-10-09T06:18:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-bal-mss-app.xlsx
+++ b/main/ig/StructureDefinition-as-bal-mss-app.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T06:18:26+00:00</t>
+    <t>2026-10-09T06:22:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
